--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T10:13:43+00:00</t>
+    <t>2023-12-15T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T15:13:16+00:00</t>
+    <t>2023-12-16T04:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T04:14:56+00:00</t>
+    <t>2023-12-16T10:12:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T10:12:57+00:00</t>
+    <t>2023-12-16T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-16T15:11:58+00:00</t>
+    <t>2023-12-17T04:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T04:15:28+00:00</t>
+    <t>2023-12-17T10:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T10:12:19+00:00</t>
+    <t>2023-12-17T15:11:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-17T15:11:55+00:00</t>
+    <t>2023-12-18T04:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T04:15:56+00:00</t>
+    <t>2023-12-18T10:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T10:14:43+00:00</t>
+    <t>2023-12-18T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T15:13:16+00:00</t>
+    <t>2023-12-19T04:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T04:15:07+00:00</t>
+    <t>2023-12-19T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:13:14+00:00</t>
+    <t>2023-12-19T15:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:12:47+00:00</t>
+    <t>2023-12-20T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T10:11:26+00:00</t>
+    <t>2023-12-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:11:12+00:00</t>
+    <t>2023-12-21T04:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T04:15:05+00:00</t>
+    <t>2023-12-21T10:13:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T10:13:12+00:00</t>
+    <t>2023-12-21T15:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T15:12:28+00:00</t>
+    <t>2023-12-22T04:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T04:14:47+00:00</t>
+    <t>2023-12-22T10:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T10:13:22+00:00</t>
+    <t>2023-12-22T15:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T15:12:35+00:00</t>
+    <t>2023-12-23T04:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T04:14:21+00:00</t>
+    <t>2023-12-23T10:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T10:12:00+00:00</t>
+    <t>2023-12-23T15:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-23T15:11:50+00:00</t>
+    <t>2023-12-24T04:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T04:14:34+00:00</t>
+    <t>2023-12-24T10:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T10:12:10+00:00</t>
+    <t>2023-12-24T15:11:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-24T15:11:47+00:00</t>
+    <t>2023-12-25T04:14:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-25T04:14:59+00:00</t>
+    <t>2023-12-25T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-25T15:13:20+00:00</t>
+    <t>2023-12-26T04:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T04:15:03+00:00</t>
+    <t>2023-12-26T10:13:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T10:13:11+00:00</t>
+    <t>2023-12-26T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T15:12:21+00:00</t>
+    <t>2023-12-28T04:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T04:15:03+00:00</t>
+    <t>2023-12-28T10:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T10:13:53+00:00</t>
+    <t>2023-12-28T15:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T15:13:05+00:00</t>
+    <t>2023-12-29T04:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T04:15:13+00:00</t>
+    <t>2023-12-29T10:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:13:25+00:00</t>
+    <t>2023-12-29T15:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T15:12:02+00:00</t>
+    <t>2023-12-30T04:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T04:15:40+00:00</t>
+    <t>2023-12-30T10:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T10:12:29+00:00</t>
+    <t>2023-12-30T15:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-30T15:11:59+00:00</t>
+    <t>2023-12-31T04:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T04:14:35+00:00</t>
+    <t>2023-12-31T10:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T10:12:20+00:00</t>
+    <t>2023-12-31T15:11:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-31T15:11:53+00:00</t>
+    <t>2024-01-01T04:15:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T04:15:30+00:00</t>
+    <t>2024-01-01T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T10:13:45+00:00</t>
+    <t>2024-01-01T15:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-01T15:12:10+00:00</t>
+    <t>2024-01-02T04:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T04:14:47+00:00</t>
+    <t>2024-01-02T10:13:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T10:13:08+00:00</t>
+    <t>2024-01-02T15:12:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-02T15:12:57+00:00</t>
+    <t>2024-01-03T04:15:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T04:15:04+00:00</t>
+    <t>2024-01-03T10:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T10:13:16+00:00</t>
+    <t>2024-01-03T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T15:12:21+00:00</t>
+    <t>2024-01-04T04:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T04:14:37+00:00</t>
+    <t>2024-01-04T10:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T10:13:28+00:00</t>
+    <t>2024-01-04T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-04T15:14:06+00:00</t>
+    <t>2024-01-05T04:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T04:15:12+00:00</t>
+    <t>2024-01-05T10:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T10:13:28+00:00</t>
+    <t>2024-01-05T15:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-05T15:13:15+00:00</t>
+    <t>2024-01-06T04:14:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T04:14:41+00:00</t>
+    <t>2024-01-06T10:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T10:12:10+00:00</t>
+    <t>2024-01-06T15:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T15:11:50+00:00</t>
+    <t>2024-01-08T04:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T04:16:08+00:00</t>
+    <t>2024-01-08T10:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T10:14:14+00:00</t>
+    <t>2024-01-09T04:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T04:15:57+00:00</t>
+    <t>2024-01-09T10:13:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T10:13:51+00:00</t>
+    <t>2024-01-09T15:13:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-09T15:13:08+00:00</t>
+    <t>2024-01-10T04:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T04:15:17+00:00</t>
+    <t>2024-01-10T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T10:13:17+00:00</t>
+    <t>2024-01-10T15:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-10T15:12:51+00:00</t>
+    <t>2024-01-11T04:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T04:15:35+00:00</t>
+    <t>2024-01-11T10:13:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T10:13:36+00:00</t>
+    <t>2024-01-11T15:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:13:05+00:00</t>
+    <t>2024-01-12T04:16:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T04:16:04+00:00</t>
+    <t>2024-01-12T10:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T10:13:42+00:00</t>
+    <t>2024-01-12T15:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T15:12:39+00:00</t>
+    <t>2024-01-13T04:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T04:15:17+00:00</t>
+    <t>2024-01-13T10:12:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T10:12:09+00:00</t>
+    <t>2024-01-13T15:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T15:12:12+00:00</t>
+    <t>2024-01-14T04:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T04:15:07+00:00</t>
+    <t>2024-01-14T10:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T10:13:00+00:00</t>
+    <t>2024-01-14T15:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T15:12:46+00:00</t>
+    <t>2024-01-15T04:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T04:16:08+00:00</t>
+    <t>2024-01-15T10:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T10:14:35+00:00</t>
+    <t>2024-01-15T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-15T15:13:20+00:00</t>
+    <t>2024-01-16T04:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T04:15:29+00:00</t>
+    <t>2024-01-16T10:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T10:13:47+00:00</t>
+    <t>2024-01-16T15:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-16T15:13:25+00:00</t>
+    <t>2024-01-17T04:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T04:15:56+00:00</t>
+    <t>2024-01-17T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T10:13:45+00:00</t>
+    <t>2024-01-17T15:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-17T15:13:25+00:00</t>
+    <t>2024-01-18T04:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T04:15:29+00:00</t>
+    <t>2024-01-18T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T10:15:26+00:00</t>
+    <t>2024-01-18T15:13:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-18T15:13:28+00:00</t>
+    <t>2024-01-19T04:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T04:15:25+00:00</t>
+    <t>2024-01-19T10:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T10:13:45+00:00</t>
+    <t>2024-01-19T15:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T15:13:27+00:00</t>
+    <t>2024-01-20T04:14:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T04:14:50+00:00</t>
+    <t>2024-01-20T10:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T10:12:15+00:00</t>
+    <t>2024-01-20T15:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-20T15:12:22+00:00</t>
+    <t>2024-01-21T04:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T04:15:25+00:00</t>
+    <t>2024-01-21T10:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T10:12:51+00:00</t>
+    <t>2024-01-21T15:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-21T15:11:52+00:00</t>
+    <t>2024-01-22T04:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T04:15:52+00:00</t>
+    <t>2024-01-22T10:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T10:14:14+00:00</t>
+    <t>2024-01-22T15:13:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T15:13:54+00:00</t>
+    <t>2024-01-23T04:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T04:15:47+00:00</t>
+    <t>2024-01-23T10:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T10:14:06+00:00</t>
+    <t>2024-01-23T15:13:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-23T15:13:43+00:00</t>
+    <t>2024-01-24T04:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-24T04:16:05+00:00</t>
+    <t>2024-01-24T10:13:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-24T10:13:46+00:00</t>
+    <t>2024-01-24T15:13:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
   <si>
     <t>Property</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>FRANCE</t>
   </si>
   <si>
     <t>Description</t>
@@ -378,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -483,68 +489,76 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>25</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>28</v>
       </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s" s="2">
         <v>33</v>
       </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s" s="2">
         <v>36</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -559,178 +573,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -745,13 +759,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -759,38 +773,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T00:00:00+02:00</t>
+    <t>2023-12-20T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19161</t>
+    <t>19151</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -121,7 +121,7 @@
     <t>Content</t>
   </si>
   <si>
-    <t>complete</t>
+    <t>not-present</t>
   </si>
   <si>
     <t>Supplements</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -88,18 +88,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>La Classification Internationale des Maladies (CIM) sert de base pour établir les tendances et les statistiques sanitaires, partout dans le monde. Elle est gérée par l’Organisation Mondiale de la Santé qui publie une mise à jour annuellement</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
     <t>Copyright</t>
   </si>
   <si>
-    <t>[CC BY-NC-ND 3.0 IGO](https://creativecommons.org/licenses/by-nc-nd/3.0/igo/legalcode)</t>
-  </si>
-  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
@@ -121,7 +115,7 @@
     <t>Content</t>
   </si>
   <si>
-    <t>not-present</t>
+    <t>complete</t>
   </si>
   <si>
     <t>Supplements</t>
@@ -489,76 +483,72 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -573,178 +563,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>23</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>65</v>
-      </c>
       <c r="D11" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>68</v>
-      </c>
       <c r="D12" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -759,13 +749,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -773,38 +763,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2024-01-01</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim-10.xlsx
@@ -115,7 +115,7 @@
     <t>Content</t>
   </si>
   <si>
-    <t>complete</t>
+    <t>not-present</t>
   </si>
   <si>
     <t>Supplements</t>
